--- a/dicc_unidades_coahuila.xlsx
+++ b/dicc_unidades_coahuila.xlsx
@@ -5,25 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\dash_control_vacunas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\dash_control_vacunas\Vacunas Coahuila\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0335CB9A-A0D1-4D99-95A3-5B66369B91FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0442F8-3E1B-4651-B93D-D608E8941A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unidades y Zonas de Coahuila" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unidades y Zonas de Coahuila'!$A$1:$B$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unidades y Zonas de Coahuila'!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>NOMBRE_UNIDAD</t>
   </si>
@@ -130,44 +131,80 @@
     <t>Farmacia UMF 93</t>
   </si>
   <si>
-    <t>U Med Familiar 23 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 25 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 27 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 28 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 29 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 30 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 31 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 32 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 50 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 60 Direccion de la Unidad Médica</t>
-  </si>
-  <si>
-    <t>U Med Familiar 4 Direccion de la Unidad Médica</t>
+    <t>Direccion UMF 14</t>
+  </si>
+  <si>
+    <t>Direccion UMF 15</t>
+  </si>
+  <si>
+    <t>Direccion UMF 26</t>
+  </si>
+  <si>
+    <t>Direccion UMF 28</t>
+  </si>
+  <si>
+    <t>Direccion UMF 29</t>
+  </si>
+  <si>
+    <t>Direccion UMF 31</t>
+  </si>
+  <si>
+    <t>Direccion UMF 32</t>
+  </si>
+  <si>
+    <t>Direccion UMF 4</t>
+  </si>
+  <si>
+    <t>Direccion UMF 50</t>
+  </si>
+  <si>
+    <t>Direccion UMF 60</t>
+  </si>
+  <si>
+    <t>Direccion UMF 61</t>
+  </si>
+  <si>
+    <t>Direccion UMF 62</t>
+  </si>
+  <si>
+    <t>Direccion UMF 64</t>
+  </si>
+  <si>
+    <t>Direccion UMF 88</t>
+  </si>
+  <si>
+    <t>Direccion UMR-EM 52</t>
+  </si>
+  <si>
+    <t>Farmacia HGSZ-MF 13</t>
+  </si>
+  <si>
+    <t>Farmacia HGSZ-MF 21</t>
+  </si>
+  <si>
+    <t>Farmacia HGSZ-MF 27</t>
+  </si>
+  <si>
+    <t>Farmacia HGSZ-MF 6</t>
+  </si>
+  <si>
+    <t>Farmacia HGZ 11</t>
+  </si>
+  <si>
+    <t>Farmacia HGZ-MF 24</t>
+  </si>
+  <si>
+    <t>Farmacia HRS Ramos</t>
+  </si>
+  <si>
+    <t>Farmacia HRS San Buenaventura</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -175,21 +212,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -197,13 +250,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,338 +490,442 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.6640625" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>3</v>
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>3</v>
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>48</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
+      </c>
+      <c r="B32" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>32</v>
+        <v>53</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>32</v>
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B40" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B40">
-      <sortCondition descending="1" ref="B1:B40"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:B1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0504E38-F20E-45B8-B427-56670567E6E1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>